--- a/data/baidu/china_scifi.xlsx
+++ b/data/baidu/china_scifi.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>银翼杀手</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>银翼杀手</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -657,24 +665,30 @@
           <t>https://movie.douban.com/subject/35267208/</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>34837.71428571428</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>流浪地球2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>流浪地球2</t>
+        </is>
+      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -734,24 +748,30 @@
           <t>https://movie.douban.com/subject/3530403/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>45919.57142857143</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>云图</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>云图</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -811,24 +831,30 @@
           <t>https://movie.douban.com/subject/34941536/</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>1818.142857142857</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>宇宙探索编辑部</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>宇宙探索编辑部</t>
+        </is>
+      </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -888,24 +914,30 @@
           <t>https://movie.douban.com/subject/26266893/</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>53317</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>流浪地球</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>流浪地球</t>
+        </is>
+      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -965,24 +997,30 @@
           <t>https://movie.douban.com/subject/3231742/</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>96667.57142857143</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>钢铁侠3</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>钢铁侠3</t>
+        </is>
+      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1045,16 +1083,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>百变星君</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>百变星君</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1122,16 +1168,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>我是谁</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>我是谁</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1199,16 +1253,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>错位</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>错位</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1273,21 +1335,27 @@
           <t>https://movie.douban.com/subject/25706773/</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>硬核亨利</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>硬核亨利</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1350,24 +1418,30 @@
           <t>https://movie.douban.com/subject/24404677/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>32082.71428571429</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>超体</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>超体</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1430,16 +1504,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>霹雳贝贝</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>霹雳贝贝</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1507,16 +1589,24 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>铠甲勇士之帝皇侠</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>铠甲勇士之帝皇侠</t>
+        </is>
+      </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
@@ -1584,16 +1674,24 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>长江七号</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>长江七号</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
@@ -1658,24 +1756,30 @@
           <t>https://movie.douban.com/subject/26816104/</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>8255.857142857143</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>从21世纪安全撤离</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>从21世纪安全撤离</t>
+        </is>
+      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1735,24 +1839,30 @@
           <t>https://movie.douban.com/subject/3168101/</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>65898.85714285714</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>毒液：致命守护者</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>毒液</t>
+        </is>
+      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1815,16 +1925,24 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>大气层消失</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>大气层消失</t>
+        </is>
+      </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
@@ -1889,24 +2007,30 @@
           <t>https://movie.douban.com/subject/36123159/</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>28587</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>熊出没·伴我“熊芯”</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1969,16 +2093,24 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>诡丝</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>诡丝</t>
+        </is>
+      </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -2046,16 +2178,24 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3393565041, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>智能大反攻</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>智能大反攻</t>
+        </is>
+      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -2120,24 +2260,30 @@
           <t>https://movie.douban.com/subject/26394152/</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>31309.42857142857</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>大黄蜂</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>大黄蜂</t>
+        </is>
+      </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2197,24 +2343,30 @@
           <t>https://movie.douban.com/subject/36970301/</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>18933.42857142857</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>熊出没·重启未来</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2274,24 +2426,30 @@
           <t>https://movie.douban.com/subject/36438166/</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>21660.85714285714</v>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>熊出没·逆转时空</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2354,16 +2512,24 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>现代豪侠传</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>现代豪侠传</t>
+        </is>
+      </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
@@ -2431,16 +2597,24 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>无限复活</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>无限复活</t>
+        </is>
+      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
@@ -2505,24 +2679,30 @@
           <t>https://movie.douban.com/subject/11502973/</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>7312.285714285715</v>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>星际特工：千星之城</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>星际特工</t>
+        </is>
+      </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -2582,24 +2762,30 @@
           <t>https://movie.douban.com/subject/30394535/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>5208</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>被光抓走的人</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>被光抓走的人</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2659,24 +2845,30 @@
           <t>https://movie.douban.com/subject/3179706/</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>12263.42857142857</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>环形使者</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>环形使者</t>
+        </is>
+      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -2736,24 +2928,30 @@
           <t>https://movie.douban.com/subject/36883105/</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>1807.428571428571</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>星河入梦</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>星河入梦</t>
+        </is>
+      </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2816,16 +3014,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>阿童木</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>阿童木</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2890,24 +3096,30 @@
           <t>https://movie.douban.com/subject/3097572/</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>13585.14285714286</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>双子杀手</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>双子杀手</t>
+        </is>
+      </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -2967,24 +3179,30 @@
           <t>https://movie.douban.com/subject/34962956/</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>7730.857142857143</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>缉魂</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>缉魂</t>
+        </is>
+      </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3047,16 +3265,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>黑侠</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>黑侠</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3121,24 +3347,30 @@
           <t>https://movie.douban.com/subject/24716039/</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>6452.571428571428</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>星际探索</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>星际探索</t>
+        </is>
+      </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3198,24 +3430,30 @@
           <t>https://movie.douban.com/subject/26967871/</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>726</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>寂静的朋友</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>寂静的朋友</t>
+        </is>
+      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3275,24 +3513,30 @@
           <t>https://movie.douban.com/subject/7054604/</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>178077.4285714286</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>变形金刚4：绝迹重生</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>变形金刚4</t>
+        </is>
+      </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -3352,24 +3596,30 @@
           <t>https://movie.douban.com/subject/3742937/</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>39461.71428571428</v>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>超级战舰</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>超级战舰</t>
+        </is>
+      </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -3429,24 +3679,30 @@
           <t>https://movie.douban.com/subject/10810745/</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>9952.428571428571</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>超验骇客</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>超验骇客</t>
+        </is>
+      </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -3506,24 +3762,30 @@
           <t>https://movie.douban.com/subject/35183042/</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>54137.85714285714</v>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -3583,24 +3845,30 @@
           <t>https://movie.douban.com/subject/25955779/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>22447.85714285714</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>忍者神龟2：破影而出</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>忍者神龟2</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3663,16 +3931,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3398739760, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>吞噬星空剧场版 血洛大陆</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>吞噬星空剧场版 血洛大陆</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3740,16 +4016,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>童梦奇缘</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>童梦奇缘</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3814,24 +4098,30 @@
           <t>https://movie.douban.com/subject/20471852/</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>43045.57142857143</v>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>生化危机：终章</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>生化危机</t>
+        </is>
+      </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -3891,24 +4181,30 @@
           <t>https://movie.douban.com/subject/35416174/</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>5264.428571428572</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>狂野时代</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>狂野时代</t>
+        </is>
+      </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -3971,16 +4267,24 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>猛鬼学堂</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>猛鬼学堂</t>
+        </is>
+      </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -4045,24 +4349,30 @@
           <t>https://movie.douban.com/subject/25986662/</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>20136.71428571429</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>疯狂的外星人</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>疯狂的外星人</t>
+        </is>
+      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -4122,24 +4432,30 @@
           <t>https://movie.douban.com/subject/25818101/</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>121708.5714285714</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>攻壳机动队</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>攻壳机动队</t>
+        </is>
+      </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -4199,24 +4515,30 @@
           <t>https://movie.douban.com/subject/24372055/</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>28342.71428571429</v>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>铠甲勇士之雅塔莱斯</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>铠甲勇士之雅塔莱斯</t>
+        </is>
+      </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -4279,16 +4601,24 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>疯狂的兔子</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>疯狂的兔子</t>
+        </is>
+      </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -4353,24 +4683,30 @@
           <t>https://movie.douban.com/subject/25838463/</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>18933.57142857143</v>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>像素大战</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>像素大战</t>
+        </is>
+      </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -4433,16 +4769,24 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>异灵灵异2002</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>异灵灵异2002</t>
+        </is>
+      </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
@@ -4510,16 +4854,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>忍者神龟</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>忍者神龟</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4587,16 +4939,24 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>魔表</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>魔表</t>
+        </is>
+      </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -4664,16 +5024,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>想飞</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>想飞</t>
+        </is>
+      </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -4738,24 +5106,30 @@
           <t>https://movie.douban.com/subject/25890017/</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>42276.14285714286</v>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>哥斯拉2：怪兽之王</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>哥斯拉2</t>
+        </is>
+      </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -4818,16 +5192,24 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>急冻奇侠</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>急冻奇侠</t>
+        </is>
+      </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
@@ -4892,24 +5274,30 @@
           <t>https://movie.douban.com/subject/34825886/</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>19345.71428571429</v>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>熊出没·狂野大陆</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>熊出没</t>
+        </is>
+      </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -4969,24 +5357,30 @@
           <t>https://movie.douban.com/subject/26353671/</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>20487.57142857143</v>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>明日战记</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>明日战记</t>
+        </is>
+      </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -5049,16 +5443,24 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>有一天</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>有一天</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
@@ -5126,16 +5528,24 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>毒吻</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>毒吻</t>
+        </is>
+      </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -5203,16 +5613,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>九一神雕侠侣</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>九一神雕侠侣</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5280,16 +5698,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>妖兽都市</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>妖兽都市</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5354,24 +5780,30 @@
           <t>https://movie.douban.com/subject/35622477/</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>1308</v>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>贝肯熊：火星任务</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>贝肯熊</t>
+        </is>
+      </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -5434,16 +5866,24 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>卫斯理传奇</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>卫斯理传奇</t>
+        </is>
+      </c>
       <c r="T65" t="n">
         <v>0</v>
       </c>
@@ -5511,16 +5951,24 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>两公婆八条心</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>两公婆八条心</t>
+        </is>
+      </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -5585,24 +6033,30 @@
           <t>https://movie.douban.com/subject/35115642/</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>3631.714285714286</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>平行森林</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>平行森林</t>
+        </is>
+      </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -5665,16 +6119,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>魔翡翠</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>魔翡翠</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5739,24 +6201,30 @@
           <t>https://movie.douban.com/subject/26219713/</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>1511.142857142857</v>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>克隆人</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>克隆人</t>
+        </is>
+      </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
@@ -5819,16 +6287,24 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>女机械人</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>女机械人</t>
+        </is>
+      </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -5893,24 +6369,30 @@
           <t>https://movie.douban.com/subject/7161695/</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>1846.714285714286</v>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>骇战</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>骇战</t>
+        </is>
+      </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -5970,24 +6452,30 @@
           <t>https://movie.douban.com/subject/27599400/</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>2377</v>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>冲出地球</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>冲出地球</t>
+        </is>
+      </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -6047,24 +6535,30 @@
           <t>https://movie.douban.com/subject/26426194/</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>11167.14285714286</v>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>巨齿鲨</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>巨齿鲨</t>
+        </is>
+      </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -6127,16 +6621,24 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>哥斯拉 终极战役</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>哥斯拉 终极战役</t>
+        </is>
+      </c>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -6201,24 +6703,30 @@
           <t>https://movie.douban.com/subject/10604087/</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>5037.142857142857</v>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>控制</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>控制</t>
+        </is>
+      </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -6278,24 +6786,30 @@
           <t>https://movie.douban.com/subject/26780023/</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>324.2857142857143</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>无限斗界之暗夜双龙</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>无限斗界之暗夜双龙</t>
+        </is>
+      </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -6355,21 +6869,27 @@
           <t>https://movie.douban.com/subject/30141681/</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>飞奔去月球</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>飞奔去月球</t>
+        </is>
+      </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6435,16 +6955,24 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>追击8月15</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>追击8月15</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -6512,16 +7040,24 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>关公大战外星人</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>关公大战外星人</t>
+        </is>
+      </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -6586,24 +7122,30 @@
           <t>https://movie.douban.com/subject/36065713/</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>6080.285714285715</v>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>超级飞侠：乐迪加速</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>超级飞侠</t>
+        </is>
+      </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -6666,16 +7208,24 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>铁甲无敌玛利亚</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>铁甲无敌玛利亚</t>
+        </is>
+      </c>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -6743,16 +7293,24 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>卫斯理之老猫</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>卫斯理之老猫</t>
+        </is>
+      </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -6817,24 +7375,30 @@
           <t>https://movie.douban.com/subject/27200988/</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>2586.285714285714</v>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>未来机器城</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>未来机器城</t>
+        </is>
+      </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -6897,16 +7461,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>基因决定我爱你</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>基因决定我爱你</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -6971,24 +7543,30 @@
           <t>https://movie.douban.com/subject/27133264/</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>7903.857142857143</v>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>海带</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>海带</t>
+        </is>
+      </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -7048,24 +7626,30 @@
           <t>https://movie.douban.com/subject/4830483/</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>4817.571428571428</v>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>喋血战士</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>喋血战士</t>
+        </is>
+      </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -7128,16 +7712,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>凶宅美人头</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>凶宅美人头</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7202,24 +7794,30 @@
           <t>https://movie.douban.com/subject/20435622/</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>24396.28571428571</v>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>环太平洋：雷霆再起</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>环太平洋</t>
+        </is>
+      </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -7279,24 +7877,30 @@
           <t>https://movie.douban.com/subject/26769592/</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>6470.571428571428</v>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>非诚勿扰3</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>非诚勿扰3</t>
+        </is>
+      </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -7359,16 +7963,24 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>珊瑚岛上的死光</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>珊瑚岛上的死光</t>
+        </is>
+      </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -7436,16 +8048,24 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>机器侠</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>机器侠</t>
+        </is>
+      </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
@@ -7513,16 +8133,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>卫斯理之蓝血人</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>卫斯理之蓝血人</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7590,16 +8218,24 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>环游地球八十天</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>环游地球八十天</t>
+        </is>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7664,24 +8300,30 @@
           <t>https://movie.douban.com/subject/11526817/</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>40253.14285714286</v>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>刺客信条</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>刺客信条</t>
+        </is>
+      </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -7744,16 +8386,24 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>中国超人</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>中国超人</t>
+        </is>
+      </c>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -7818,24 +8468,30 @@
           <t>https://movie.douban.com/subject/26825482/</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>9913.857142857143</v>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>月球陨落</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>月球陨落</t>
+        </is>
+      </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -7895,21 +8551,27 @@
           <t>https://movie.douban.com/subject/37060861/</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>盒中之海</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>盒中之海</t>
+        </is>
+      </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -7968,24 +8630,30 @@
           <t>https://movie.douban.com/subject/37298398/</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>2010.714285714286</v>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>海底小纵队：海啸大危机</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>海底小纵队</t>
+        </is>
+      </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -8048,16 +8716,24 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3425832958, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>小胖妞前传（上）</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>小胖妞前传</t>
+        </is>
+      </c>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -8122,24 +8798,30 @@
           <t>https://movie.douban.com/subject/35496650/</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>1439</v>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>舒克贝塔·五角飞碟</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>舒克贝塔</t>
+        </is>
+      </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -8199,24 +8881,30 @@
           <t>https://movie.douban.com/subject/21943062/</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>4963.714285714285</v>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>黑猫警长之翡翠之星</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>黑猫警长之翡翠之星</t>
+        </is>
+      </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -8276,24 +8964,30 @@
           <t>https://movie.douban.com/subject/30382416/</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>9000.142857142857</v>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>毒液2</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>毒液2</t>
+        </is>
+      </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -8356,16 +9050,24 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3427006964, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>吃货宇宙</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>吃货宇宙</t>
+        </is>
+      </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
@@ -8430,21 +9132,27 @@
           <t>https://movie.douban.com/subject/30402063/</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>太空群落</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>太空群落</t>
+        </is>
+      </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -8510,16 +9218,24 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>北海怪兽</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>北海怪兽</t>
+        </is>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8584,24 +9300,30 @@
           <t>https://movie.douban.com/subject/6799156/</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>3455.857142857143</v>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>超时空救兵</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>超时空救兵</t>
+        </is>
+      </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -8664,16 +9386,24 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>合成人</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>合成人</t>
+        </is>
+      </c>
       <c r="T107" t="n">
         <v>0</v>
       </c>
@@ -8738,24 +9468,30 @@
           <t>https://movie.douban.com/subject/26331608/</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>1319.714285714286</v>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>桂宝之爆笑闯宇宙</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>桂宝之爆笑闯宇宙</t>
+        </is>
+      </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -8815,24 +9551,30 @@
           <t>https://movie.douban.com/subject/34882958/</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>14254.14285714286</v>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>巨齿鲨2：深渊</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>巨齿鲨2</t>
+        </is>
+      </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -8892,24 +9634,30 @@
           <t>https://movie.douban.com/subject/5324813/</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>460.4285714285714</v>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>天际浩劫2</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>天际浩劫2</t>
+        </is>
+      </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -8969,24 +9717,30 @@
           <t>https://movie.douban.com/subject/26707077/</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>148.2857142857143</v>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>幸福城市</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>幸福城市</t>
+        </is>
+      </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -9049,16 +9803,24 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>忍者神龟2</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>忍者神龟2</t>
+        </is>
+      </c>
       <c r="T112" t="n">
         <v>0</v>
       </c>
@@ -9126,16 +9888,24 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>朝花夕拾</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>朝花夕拾</t>
+        </is>
+      </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
@@ -9203,16 +9973,24 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>拳神</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>拳神</t>
+        </is>
+      </c>
       <c r="T114" t="n">
         <v>0</v>
       </c>
@@ -9277,24 +10055,30 @@
           <t>https://movie.douban.com/subject/25824686/</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>82723.57142857143</v>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>变形金刚5：最后的骑士</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>变形金刚5</t>
+        </is>
+      </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -9357,16 +10141,24 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3429456356, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>开心超人之时空营救</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>开心超人之时空营救</t>
+        </is>
+      </c>
       <c r="T116" t="n">
         <v>0</v>
       </c>
@@ -9431,21 +10223,27 @@
           <t>https://movie.douban.com/subject/34661803/</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>烈阳天道</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>烈阳天道</t>
+        </is>
+      </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -9511,16 +10309,24 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>隐身博士</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>隐身博士</t>
+        </is>
+      </c>
       <c r="T118" t="n">
         <v>0</v>
       </c>
@@ -9585,24 +10391,30 @@
           <t>https://movie.douban.com/subject/26724807/</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
+      <c r="O119" t="n">
+        <v>2560.714285714286</v>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>24小时：末路重生</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>24小时</t>
+        </is>
+      </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
@@ -9665,16 +10477,24 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>男人的世界</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>男人的世界</t>
+        </is>
+      </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
@@ -9735,24 +10555,30 @@
           <t>https://movie.douban.com/subject/26897547/</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
+      <c r="O121" t="n">
+        <v>3925.714285714286</v>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>孤岛终结</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>孤岛终结</t>
+        </is>
+      </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -9815,16 +10641,24 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3430599647, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>最后的日出</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>最后的日出</t>
+        </is>
+      </c>
       <c r="T122" t="n">
         <v>0</v>
       </c>
@@ -9889,24 +10723,30 @@
           <t>https://movie.douban.com/subject/35936420/</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
+      <c r="O123" t="n">
+        <v>3569.571428571428</v>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>鬼吹灯之精绝古城</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>鬼吹灯之精绝古城</t>
+        </is>
+      </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -9969,16 +10809,24 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>黑侠2</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>黑侠2</t>
+        </is>
+      </c>
       <c r="T124" t="n">
         <v>0</v>
       </c>
@@ -10046,16 +10894,24 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>忍者神龟3</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>忍者神龟3</t>
+        </is>
+      </c>
       <c r="T125" t="n">
         <v>0</v>
       </c>
@@ -10120,24 +10976,30 @@
           <t>https://movie.douban.com/subject/26277156/</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" t="n">
+        <v>3202.857142857143</v>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>不可思异</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>不可思异</t>
+        </is>
+      </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
@@ -10197,24 +11059,30 @@
           <t>https://movie.douban.com/subject/34458481/</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr"/>
+      <c r="O127" t="n">
+        <v>382.8571428571428</v>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>新星</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>新星</t>
+        </is>
+      </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
@@ -10277,16 +11145,24 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3431624196, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>复身犯</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>复身犯</t>
+        </is>
+      </c>
       <c r="T128" t="n">
         <v>0</v>
       </c>
@@ -10350,16 +11226,24 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>绿色食品</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>绿色食品</t>
+        </is>
+      </c>
       <c r="T129" t="n">
         <v>0</v>
       </c>
@@ -10424,24 +11308,30 @@
           <t>https://movie.douban.com/subject/30299388/</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="n">
+        <v>10116.42857142857</v>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>天才J之谜题里的倒计时</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>天才J之谜题里的倒计时</t>
+        </is>
+      </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -10504,16 +11394,24 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>小太阳</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>小太阳</t>
+        </is>
+      </c>
       <c r="T131" t="n">
         <v>0</v>
       </c>
@@ -10578,24 +11476,30 @@
           <t>https://movie.douban.com/subject/26667056/</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="n">
+        <v>7565.285714285715</v>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>逆时营救</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>逆时营救</t>
+        </is>
+      </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -10658,16 +11562,24 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>全城戒备</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>全城戒备</t>
+        </is>
+      </c>
       <c r="T133" t="n">
         <v>0</v>
       </c>
@@ -10735,16 +11647,24 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3432694418, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>烈阳天道Ⅱ</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>烈阳天道Ⅱ</t>
+        </is>
+      </c>
       <c r="T134" t="n">
         <v>0</v>
       </c>
@@ -10812,16 +11732,24 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>超强台风</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>超强台风</t>
+        </is>
+      </c>
       <c r="T135" t="n">
         <v>0</v>
       </c>
@@ -10886,24 +11814,30 @@
           <t>https://movie.douban.com/subject/26729868/</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="O136" t="n">
+        <v>11622.28571428571</v>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>机器之血</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>机器之血</t>
+        </is>
+      </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -10963,24 +11897,30 @@
           <t>https://movie.douban.com/subject/26807960/</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" t="n">
+        <v>275.4285714285714</v>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>所爱非人</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>所爱非人</t>
+        </is>
+      </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -11040,21 +11980,27 @@
           <t>https://movie.douban.com/subject/30481964/</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>艾特所有人</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>艾特所有人</t>
+        </is>
+      </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -11120,16 +12066,24 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3433858631, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>比如父子</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>比如父子</t>
+        </is>
+      </c>
       <c r="T139" t="n">
         <v>0</v>
       </c>
@@ -11197,16 +12151,24 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>猩猩王</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>猩猩王</t>
+        </is>
+      </c>
       <c r="T140" t="n">
         <v>0</v>
       </c>
@@ -11271,24 +12233,30 @@
           <t>https://movie.douban.com/subject/6796160/</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="n">
+        <v>14822.28571428571</v>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时33D</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>蜜桃成熟时33D</t>
+        </is>
+      </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
@@ -11351,16 +12319,24 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>魔殿屠龙</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>魔殿屠龙</t>
+        </is>
+      </c>
       <c r="T142" t="n">
         <v>0</v>
       </c>
@@ -11428,16 +12404,24 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3434411693, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>银河守卫队</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>银河守卫队</t>
+        </is>
+      </c>
       <c r="T143" t="n">
         <v>0</v>
       </c>
@@ -11505,16 +12489,24 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3434683027, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>不倒侠</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>不倒侠</t>
+        </is>
+      </c>
       <c r="T144" t="n">
         <v>0</v>
       </c>
@@ -11579,24 +12571,30 @@
           <t>https://movie.douban.com/subject/36597039/</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="n">
+        <v>266.7142857142857</v>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>猪猪侠大电影·星际行动</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>猪猪侠大电影</t>
+        </is>
+      </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -11656,24 +12654,30 @@
           <t>https://movie.douban.com/subject/25881615/</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
+      <c r="O146" t="n">
+        <v>9820</v>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>超凡战队</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>超凡战队</t>
+        </is>
+      </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
@@ -11736,16 +12740,24 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3435449327, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>程序恋人</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>程序恋人</t>
+        </is>
+      </c>
       <c r="T147" t="n">
         <v>0</v>
       </c>
@@ -11813,16 +12825,24 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>魔比斯环</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>魔比斯环</t>
+        </is>
+      </c>
       <c r="T148" t="n">
         <v>0</v>
       </c>
@@ -11887,24 +12907,30 @@
           <t>https://movie.douban.com/subject/27056322/</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="n">
+        <v>235.7142857142857</v>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>花悸</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>花悸</t>
+        </is>
+      </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -11963,16 +12989,24 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>爆炸性新闻</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>爆炸性新闻</t>
+        </is>
+      </c>
       <c r="T150" t="n">
         <v>0</v>
       </c>
@@ -12036,16 +13070,24 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3436037649, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>完美的死法</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>完美的死法</t>
+        </is>
+      </c>
       <c r="T151" t="n">
         <v>0</v>
       </c>
@@ -12110,24 +13152,30 @@
           <t>https://movie.douban.com/subject/35295013/</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr"/>
+      <c r="O152" t="n">
+        <v>2183.142857142857</v>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>狩猎</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>狩猎</t>
+        </is>
+      </c>
       <c r="T152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
@@ -12190,16 +13238,24 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>戆星先生</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>戆星先生</t>
+        </is>
+      </c>
       <c r="T153" t="n">
         <v>0</v>
       </c>
@@ -12263,16 +13319,24 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>空谷十年</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>空谷十年</t>
+        </is>
+      </c>
       <c r="T154" t="n">
         <v>0</v>
       </c>
@@ -12340,16 +13404,24 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>星际钝胎</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>星际钝胎</t>
+        </is>
+      </c>
       <c r="T155" t="n">
         <v>0</v>
       </c>
@@ -12414,24 +13486,30 @@
           <t>https://movie.douban.com/subject/35168646/</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr"/>
+      <c r="O156" t="n">
+        <v>6609.142857142857</v>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>外太空的莫扎特</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>外太空的莫扎特</t>
+        </is>
+      </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -12491,24 +13569,30 @@
           <t>https://movie.douban.com/subject/35043230/</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr"/>
+      <c r="O157" t="n">
+        <v>3091</v>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>神兵特攻</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>神兵特攻</t>
+        </is>
+      </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -12571,16 +13655,24 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3437221857, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>订制男友</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>订制男友</t>
+        </is>
+      </c>
       <c r="T158" t="n">
         <v>0</v>
       </c>
@@ -12645,24 +13737,30 @@
           <t>https://movie.douban.com/subject/24872197/</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="n">
+        <v>1046.714285714286</v>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>来历不明</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>来历不明</t>
+        </is>
+      </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -12722,24 +13820,30 @@
           <t>https://movie.douban.com/subject/26602368/</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr"/>
+      <c r="O160" t="n">
+        <v>1320.285714285714</v>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>我的极品女神</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>我的极品女神</t>
+        </is>
+      </c>
       <c r="T160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -12799,24 +13903,30 @@
           <t>https://movie.douban.com/subject/35089826/</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
+      <c r="O161" t="n">
+        <v>605.7142857142857</v>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>铁甲狂猴之亡命雷霆</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>铁甲狂猴之亡命雷霆</t>
+        </is>
+      </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U161" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -12876,21 +13986,27 @@
           <t>https://movie.douban.com/subject/35248741/</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>沙丘虫暴</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>沙丘虫暴</t>
+        </is>
+      </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -12956,16 +14072,24 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>超蛙战士之初露锋芒</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>超蛙战士之初露锋芒</t>
+        </is>
+      </c>
       <c r="T163" t="n">
         <v>0</v>
       </c>
@@ -13033,16 +14157,24 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>未来警察</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>未来警察</t>
+        </is>
+      </c>
       <c r="T164" t="n">
         <v>0</v>
       </c>
@@ -13107,24 +14239,30 @@
           <t>https://movie.douban.com/subject/35295101/</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="O165" t="n">
+        <v>319.4285714285714</v>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>猎毒者</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>猎毒者</t>
+        </is>
+      </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U165" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
@@ -13187,16 +14325,24 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3468202644, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>朱雀战纪</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>朱雀战纪</t>
+        </is>
+      </c>
       <c r="T166" t="n">
         <v>0</v>
       </c>
@@ -13261,24 +14407,30 @@
           <t>https://movie.douban.com/subject/27052551/</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
+      <c r="O167" t="n">
+        <v>3092.571428571428</v>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>超级APP</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>超级APP</t>
+        </is>
+      </c>
       <c r="T167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
@@ -13338,21 +14490,27 @@
           <t>https://movie.douban.com/subject/35559713/</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>大画王</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>大画王</t>
+        </is>
+      </c>
       <c r="T168" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -13418,16 +14576,24 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3468972295, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>星际流浪</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>星际流浪</t>
+        </is>
+      </c>
       <c r="T169" t="n">
         <v>0</v>
       </c>
@@ -13492,24 +14658,30 @@
           <t>https://movie.douban.com/subject/26921002/</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr"/>
+      <c r="O170" t="n">
+        <v>240</v>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>决战异世界</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>决战异世界</t>
+        </is>
+      </c>
       <c r="T170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -13569,24 +14741,30 @@
           <t>https://movie.douban.com/subject/35515217/</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="n">
+        <v>1285.714285714286</v>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>战地：异种浩劫</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>战地</t>
+        </is>
+      </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -13646,24 +14824,30 @@
           <t>https://movie.douban.com/subject/30317800/</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr"/>
+      <c r="O172" t="n">
+        <v>1306</v>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>怪兽</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>怪兽</t>
+        </is>
+      </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -13726,16 +14910,24 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3470504751, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>宇宙有爱浪漫同游</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>宇宙有爱浪漫同游</t>
+        </is>
+      </c>
       <c r="T173" t="n">
         <v>0</v>
       </c>
@@ -13800,24 +14992,30 @@
           <t>https://movie.douban.com/subject/35447154/</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr"/>
+      <c r="O174" t="n">
+        <v>3560.714285714286</v>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>大蛇3：龙蛇之战</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>大蛇3</t>
+        </is>
+      </c>
       <c r="T174" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U174" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -13880,16 +15078,24 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>力王中王</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>力王中王</t>
+        </is>
+      </c>
       <c r="T175" t="n">
         <v>0</v>
       </c>
@@ -13954,24 +15160,30 @@
           <t>https://movie.douban.com/subject/27191370/</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr"/>
+      <c r="O176" t="n">
+        <v>1588.285714285714</v>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>终极代码</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>终极代码</t>
+        </is>
+      </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U176" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -14031,24 +15243,30 @@
           <t>https://movie.douban.com/subject/26826370/</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
+      <c r="O177" t="n">
+        <v>1827.142857142857</v>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>如来神掌</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>如来神掌</t>
+        </is>
+      </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -14108,24 +15326,30 @@
           <t>https://movie.douban.com/subject/34868338/</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr"/>
+      <c r="O178" t="n">
+        <v>681.2857142857143</v>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>蟑潮</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>蟑潮</t>
+        </is>
+      </c>
       <c r="T178" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -14188,16 +15412,24 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3471858514, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>怪兽湖</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>怪兽湖</t>
+        </is>
+      </c>
       <c r="T179" t="n">
         <v>0</v>
       </c>
@@ -14262,24 +15494,30 @@
           <t>https://movie.douban.com/subject/34953858/</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
+      <c r="O180" t="n">
+        <v>596.7142857142857</v>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>外星人事件</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>外星人事件</t>
+        </is>
+      </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U180" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -14339,21 +15577,27 @@
           <t>https://movie.douban.com/subject/30345341/</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr"/>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>动物出击</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>动物出击</t>
+        </is>
+      </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U181" t="n">
         <v>0</v>
@@ -14419,16 +15663,24 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>七龙珠</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>七龙珠</t>
+        </is>
+      </c>
       <c r="T182" t="n">
         <v>0</v>
       </c>
@@ -14493,21 +15745,27 @@
           <t>https://movie.douban.com/subject/35043875/</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr"/>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>罗布泊神秘事件</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>罗布泊神秘事件</t>
+        </is>
+      </c>
       <c r="T183" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U183" t="n">
         <v>0</v>
@@ -14570,24 +15828,30 @@
           <t>https://movie.douban.com/subject/26677141/</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="n">
+        <v>3038.428571428572</v>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>伊阿索密码</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>伊阿索密码</t>
+        </is>
+      </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U184" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185">
@@ -14647,24 +15911,30 @@
           <t>https://movie.douban.com/subject/36597293/</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr"/>
+      <c r="O185" t="n">
+        <v>1345.428571428571</v>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>章鲨</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>章鲨</t>
+        </is>
+      </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U185" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -14724,24 +15994,30 @@
           <t>https://movie.douban.com/subject/35411088/</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
+      <c r="O186" t="n">
+        <v>5278.571428571428</v>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>重启地球</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>重启地球</t>
+        </is>
+      </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U186" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
@@ -14801,24 +16077,30 @@
           <t>https://movie.douban.com/subject/27180936/</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
+      <c r="O187" t="n">
+        <v>3703.285714285714</v>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>超自然事件之坠龙事件</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>超自然事件之坠龙事件</t>
+        </is>
+      </c>
       <c r="T187" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U187" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -14878,24 +16160,30 @@
           <t>https://movie.douban.com/subject/35027723/</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
+      <c r="O188" t="n">
+        <v>1115.142857142857</v>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>火星异变</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>火星异变</t>
+        </is>
+      </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U188" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189">
@@ -14958,16 +16246,24 @@
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3474331884, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>太空熊猫英雄归来</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>太空熊猫英雄归来</t>
+        </is>
+      </c>
       <c r="T189" t="n">
         <v>0</v>
       </c>
@@ -15032,24 +16328,30 @@
           <t>https://movie.douban.com/subject/26285355/</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr"/>
+      <c r="O190" t="n">
+        <v>666.5714285714286</v>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>时光大战</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>时光大战</t>
+        </is>
+      </c>
       <c r="T190" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U190" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191">
@@ -15112,16 +16414,24 @@
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3474783067, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>功夫机器侠之北腿</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>功夫机器侠之北腿</t>
+        </is>
+      </c>
       <c r="T191" t="n">
         <v>0</v>
       </c>
@@ -15186,24 +16496,30 @@
           <t>https://movie.douban.com/subject/35092721/</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr"/>
+      <c r="O192" t="n">
+        <v>602.7142857142857</v>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>机械画皮</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>机械画皮</t>
+        </is>
+      </c>
       <c r="T192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
@@ -15263,21 +16579,27 @@
           <t>https://movie.douban.com/subject/35860951/</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr"/>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>环线</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>环线</t>
+        </is>
+      </c>
       <c r="T193" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U193" t="n">
         <v>0</v>
@@ -15343,16 +16665,24 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>变异危机</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>变异危机</t>
+        </is>
+      </c>
       <c r="T194" t="n">
         <v>0</v>
       </c>
@@ -15420,16 +16750,24 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3475556806, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>电磁王之霹雳父子</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>电磁王之霹雳父子</t>
+        </is>
+      </c>
       <c r="T195" t="n">
         <v>0</v>
       </c>
@@ -15494,24 +16832,30 @@
           <t>https://movie.douban.com/subject/35196786/</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr"/>
+      <c r="O196" t="n">
+        <v>659.7142857142857</v>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>大章鱼</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>大章鱼</t>
+        </is>
+      </c>
       <c r="T196" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U196" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -15571,24 +16915,30 @@
           <t>https://movie.douban.com/subject/26381387/</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr"/>
+      <c r="O197" t="n">
+        <v>698.5714285714286</v>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>超能兔战队</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>超能兔战队</t>
+        </is>
+      </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U197" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -15648,24 +16998,30 @@
           <t>https://movie.douban.com/subject/34433857/</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr"/>
+      <c r="O198" t="n">
+        <v>6809.714285714285</v>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>我的女友是机器人</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>我的女友是机器人</t>
+        </is>
+      </c>
       <c r="T198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -15725,24 +17081,30 @@
           <t>https://movie.douban.com/subject/35295114/</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
+      <c r="O199" t="n">
+        <v>3767.571428571428</v>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>末日救援</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>末日救援</t>
+        </is>
+      </c>
       <c r="T199" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U199" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -15802,24 +17164,30 @@
           <t>https://movie.douban.com/subject/25958914/</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
+      <c r="O200" t="n">
+        <v>4316.571428571428</v>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>食人虫</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>食人虫</t>
+        </is>
+      </c>
       <c r="T200" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U200" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -15879,24 +17247,30 @@
           <t>https://movie.douban.com/subject/26790117/</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr"/>
+      <c r="O201" t="n">
+        <v>6959.714285714285</v>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>功夫机器侠</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>功夫机器侠</t>
+        </is>
+      </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -15956,24 +17330,30 @@
           <t>https://movie.douban.com/subject/30190607/</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr"/>
+      <c r="O202" t="n">
+        <v>3956.714285714286</v>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>钢铁飞龙之奥特曼崛起</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>钢铁飞龙之奥特曼崛起</t>
+        </is>
+      </c>
       <c r="T202" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U202" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203">
@@ -16036,16 +17416,24 @@
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3477935390, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>锤神</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>锤神</t>
+        </is>
+      </c>
       <c r="T203" t="n">
         <v>0</v>
       </c>
@@ -16113,16 +17501,24 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3478098895, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>火星归来</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>火星归来</t>
+        </is>
+      </c>
       <c r="T204" t="n">
         <v>0</v>
       </c>
@@ -16187,21 +17583,27 @@
           <t>https://movie.douban.com/subject/33383459/</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr"/>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>记忆切割</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>记忆切割</t>
+        </is>
+      </c>
       <c r="T205" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U205" t="n">
         <v>0</v>
@@ -16264,24 +17666,30 @@
           <t>https://movie.douban.com/subject/26279449/</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr"/>
+      <c r="O206" t="n">
+        <v>17935.85714285714</v>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>蒸发太平洋</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>蒸发太平洋</t>
+        </is>
+      </c>
       <c r="T206" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U206" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207">
@@ -16341,24 +17749,30 @@
           <t>https://movie.douban.com/subject/10756744/</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr"/>
+      <c r="O207" t="n">
+        <v>7982.285714285715</v>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>史前怪兽</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>史前怪兽</t>
+        </is>
+      </c>
       <c r="T207" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U207" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208">
@@ -16418,24 +17832,30 @@
           <t>https://movie.douban.com/subject/2130529/</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr"/>
+      <c r="O208" t="n">
+        <v>12510</v>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>拳皇</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>拳皇</t>
+        </is>
+      </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -16495,24 +17915,30 @@
           <t>https://movie.douban.com/subject/26747919/</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr"/>
+      <c r="O209" t="n">
+        <v>49718.85714285714</v>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>749局</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>749局</t>
+        </is>
+      </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -16572,21 +17998,27 @@
           <t>https://movie.douban.com/subject/26850330/</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>欲念游戏</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>欲念游戏</t>
+        </is>
+      </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U210" t="n">
         <v>0</v>
@@ -16649,24 +18081,30 @@
           <t>https://movie.douban.com/subject/27045442/</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr"/>
+      <c r="O211" t="n">
+        <v>4385.714285714285</v>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>钢铁飞龙之再见奥特曼</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>钢铁飞龙之再见奥特曼</t>
+        </is>
+      </c>
       <c r="T211" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U211" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212">
@@ -16726,24 +18164,30 @@
           <t>https://movie.douban.com/subject/26581837/</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr"/>
+      <c r="O212" t="n">
+        <v>31727.28571428571</v>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>上海堡垒</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>上海堡垒</t>
+        </is>
+      </c>
       <c r="T212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
